--- a/GeoSimp_test.xlsx
+++ b/GeoSimp_test.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MATERIAL TRABAJO\CIENCIA DE DATOS PROYECTOS\detection similar sentences\text simplification2\dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MATERIAL TRABAJO\CIENCIA DE DATOS PROYECTOS\SIMPLIFICACION -2\PaperDataset\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56726AC7-4F29-477B-8EF4-3634EEAEA1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{344F7187-86E8-4455-99C3-CE9FE75D008C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="10296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="References" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="2457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="2458">
   <si>
     <t>id</t>
   </si>
@@ -7396,13 +7397,16 @@
   </si>
   <si>
     <t>[14]</t>
+  </si>
+  <si>
+    <t>[14] G. E. Alvarado and A. Vargas, “Historia del descubrimiento y aprovechamiento de las fuentes termales en Costa Rica,” Revista Geológica de América Central, no. 57, Sep. 2017, doi: 10.15517/rgac.v0i57.30148. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7414,6 +7418,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -7454,11 +7465,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19667,4 +19681,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D700A3BF-39F2-4F95-BF1C-2308B1460ED9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="49.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>